--- a/tools/importer/reports/import-figma-site-template.report.xlsx
+++ b/tools/importer/reports/import-figma-site-template.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="29">
   <si>
     <t>_reportFile</t>
   </si>
@@ -59,6 +59,24 @@
   </si>
   <si>
     <t>http://localhost:8765/en/figma-site-template-1.html</t>
+  </si>
+  <si>
+    <t>en/figma-site-template-2.report.json</t>
+  </si>
+  <si>
+    <t>["ssn","hero (mds)","jump-links","columns","hero (mds, campaign)","cards (mds, product)","columns","accordion (mds)","cards (mds)","cards (mds)"]</t>
+  </si>
+  <si>
+    <t>en/figma-site-template-2</t>
+  </si>
+  <si>
+    <t>2026-10-07T16:18:00.114Z</t>
+  </si>
+  <si>
+    <t>Application Page Title | 3M United States</t>
+  </si>
+  <si>
+    <t>http://localhost:8765/en/figma-site-template-2.html</t>
   </si>
   <si>
     <t>3m/en-us/government-us.report.json</t>
@@ -468,7 +486,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -545,16 +563,42 @@
         <v>11</v>
       </c>
       <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
         <v>19</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>20</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>21</v>
       </c>
-      <c r="H3" t="s">
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
